--- a/tools/importer/reports/import-press-releases-listing.report.xlsx
+++ b/tools/importer/reports/import-press-releases-listing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="64">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,157 @@
     <t>press-releases-listing</t>
   </si>
   <si>
-    <t>2026-07-08T11:02:41.128Z</t>
+    <t>2026-07-12T14:14:02.622Z</t>
   </si>
   <si>
     <t>Comunicate de presă | Romgaz</t>
   </si>
   <si>
     <t>https://romgaz.ro/comunicate-de-presa</t>
+  </si>
+  <si>
+    <t>grupul-romgaz-publicat-raportul-anual-consolidat-preliminar-pentru-anul-2025.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>grupul-romgaz-publicat-raportul-anual-consolidat-preliminar-pentru-anul-2025</t>
+  </si>
+  <si>
+    <t>press-release-article</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:58:56.991Z</t>
+  </si>
+  <si>
+    <t>Grupul ROMGAZ a publicat Raportul anual consolidat preliminar pentru anul 2025 | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/grupul-romgaz-publicat-raportul-anual-consolidat-preliminar-pentru-anul-2025</t>
+  </si>
+  <si>
+    <t>noutati-si-evenimente.report.json</t>
+  </si>
+  <si>
+    <t>noutati-si-evenimente</t>
+  </si>
+  <si>
+    <t>news-events-hub</t>
+  </si>
+  <si>
+    <t>2026-07-08T11:02:54.331Z</t>
+  </si>
+  <si>
+    <t>Noutăți și evenimente | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/noutati-si-evenimente</t>
+  </si>
+  <si>
+    <t>progres-cadrul-neptun-deep-incep-lucrarile-de-instalare-conductei-de-gaze-marea-neagra.report.json</t>
+  </si>
+  <si>
+    <t>progres-cadrul-neptun-deep-incep-lucrarile-de-instalare-conductei-de-gaze-marea-neagra</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:58:51.612Z</t>
+  </si>
+  <si>
+    <t>Progres în cadrul Neptun Deep: încep lucrările de instalare a conductei de gaze în Marea Neagră | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/progres-cadrul-neptun-deep-incep-lucrarile-de-instalare-conductei-de-gaze-marea-neagra</t>
+  </si>
+  <si>
+    <t>romgaz-continua-angajamentul-ferm-de-investitii-de-explorare-perimetrul-neptun-deep-din-marea.report.json</t>
+  </si>
+  <si>
+    <t>romgaz-continua-angajamentul-ferm-de-investitii-de-explorare-perimetrul-neptun-deep-din-marea</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:59:12.801Z</t>
+  </si>
+  <si>
+    <t>ROMGAZ continuă angajamentul ferm de investiții de explorare în perimetrul Neptun Deep din Marea Neagră | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/romgaz-continua-angajamentul-ferm-de-investitii-de-explorare-perimetrul-neptun-deep-din-marea</t>
+  </si>
+  <si>
+    <t>romgaz-face-precizari-fata-de-informarea-de-presa-azomures.report.json</t>
+  </si>
+  <si>
+    <t>romgaz-face-precizari-fata-de-informarea-de-presa-azomures</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:59:02.607Z</t>
+  </si>
+  <si>
+    <t>ROMGAZ face precizări față de informarea de presă a Azomureș | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/romgaz-face-precizari-fata-de-informarea-de-presa-azomures</t>
+  </si>
+  <si>
+    <t>romgaz-incheie-un-parteneriat-strategic-cu-weatherford-pentru-digitalizarea-operatiunilor-de.report.json</t>
+  </si>
+  <si>
+    <t>romgaz-incheie-un-parteneriat-strategic-cu-weatherford-pentru-digitalizarea-operatiunilor-de</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:59:25.250Z</t>
+  </si>
+  <si>
+    <t>ROMGAZ încheie un parteneriat strategic cu Weatherford pentru digitalizarea operațiunilor de producție | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/romgaz-incheie-un-parteneriat-strategic-cu-weatherford-pentru-digitalizarea-operatiunilor-de</t>
+  </si>
+  <si>
+    <t>romgaz-listeaza-cea-de-doua-emisiune-de-obligatiuni-la-bursa-de-valori-bucuresti-valoare-de-500.report.json</t>
+  </si>
+  <si>
+    <t>romgaz-listeaza-cea-de-doua-emisiune-de-obligatiuni-la-bursa-de-valori-bucuresti-valoare-de-500</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:59:07.841Z</t>
+  </si>
+  <si>
+    <t>ROMGAZ listează cea de-a doua emisiune de obligațiuni la Bursa de Valori București, în valoare de 500 milioane de euro | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/romgaz-listeaza-cea-de-doua-emisiune-de-obligatiuni-la-bursa-de-valori-bucuresti-valoare-de-500</t>
+  </si>
+  <si>
+    <t>romgaz-publicat-raportul-trimestrial-privind-activitatea-economico-financiara-grupului-romgaz-la-30.report.json</t>
+  </si>
+  <si>
+    <t>romgaz-publicat-raportul-trimestrial-privind-activitatea-economico-financiara-grupului-romgaz-la-30</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:59:19.204Z</t>
+  </si>
+  <si>
+    <t>ROMGAZ a publicat Raportul trimestrial privind activitatea economico-financiară a Grupului ROMGAZ la 30 septembrie 2025 (perioada 01.01.2025 – 30.09.2025) | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/romgaz-publicat-raportul-trimestrial-privind-activitatea-economico-financiara-grupului-romgaz-la-30</t>
+  </si>
+  <si>
+    <t>romgaz-publicat-raportul-trimestrial-privind-activitatea-economico-financiara-grupului-romgaz-la-31.report.json</t>
+  </si>
+  <si>
+    <t>romgaz-publicat-raportul-trimestrial-privind-activitatea-economico-financiara-grupului-romgaz-la-31</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:58:44.858Z</t>
+  </si>
+  <si>
+    <t>ROMGAZ a publicat Raportul trimestrial privind activitatea economico-financiară a Grupului ROMGAZ la 31 martie 2026 | Romgaz</t>
+  </si>
+  <si>
+    <t>https://romgaz.ro/romgaz-publicat-raportul-trimestrial-privind-activitatea-economico-financiara-grupului-romgaz-la-31</t>
   </si>
 </sst>
 </file>
@@ -447,16 +591,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="39" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +652,240 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
